--- a/docs/downloads/05/tbl_agri_equip_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_marovoay_tous.xlsx
@@ -472,12 +472,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -526,12 +520,6 @@
           <t>Filet</t>
         </is>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -580,12 +568,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -598,12 +580,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -616,12 +592,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +604,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +616,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +628,6 @@
           <t>Soubique, produits de tis</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -737,12 +689,6 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -755,12 +701,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -809,12 +749,6 @@
           <t>Canne planteuse</t>
         </is>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -827,12 +761,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -881,12 +809,6 @@
           <t>Décortiqueur / dépailleur</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -935,12 +857,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -971,12 +887,6 @@
           <t>Houe</t>
         </is>
       </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -989,12 +899,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1025,12 +929,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1043,12 +941,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1110,12 +1002,6 @@
           <t>Arrosoir/Sceau</t>
         </is>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1128,12 +1014,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1146,12 +1026,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1182,12 +1056,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1236,12 +1104,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1290,12 +1152,6 @@
           <t>Filet</t>
         </is>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1380,12 +1236,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1398,12 +1248,6 @@
           <t>Râteau, fourche</t>
         </is>
       </c>
-      <c r="C59">
-        <v>2</v>
-      </c>
-      <c r="D59">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1416,12 +1260,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1434,12 +1272,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1470,12 +1302,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1519,12 +1345,6 @@
           <t>Arrosoir/Sceau</t>
         </is>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1537,12 +1357,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1555,12 +1369,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1573,12 +1381,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C69">
-        <v>2</v>
-      </c>
-      <c r="D69">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1681,12 +1483,6 @@
           <t>Filet</t>
         </is>
       </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-      <c r="D75">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1717,12 +1513,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C77">
-        <v>3</v>
-      </c>
-      <c r="D77">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1753,12 +1543,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C79">
-        <v>2</v>
-      </c>
-      <c r="D79">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1771,12 +1555,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1789,12 +1567,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1807,12 +1579,6 @@
           <t>Râteau, fourche</t>
         </is>
       </c>
-      <c r="C82">
-        <v>2</v>
-      </c>
-      <c r="D82">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1825,12 +1591,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1843,12 +1603,6 @@
           <t>Soubique, produits de tis</t>
         </is>
       </c>
-      <c r="C84">
-        <v>2</v>
-      </c>
-      <c r="D84">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1861,12 +1615,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1928,12 +1676,6 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1946,12 +1688,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C90">
-        <v>3</v>
-      </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1982,12 +1718,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C92">
-        <v>3</v>
-      </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2018,12 +1748,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94">
-        <v>0</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2036,12 +1760,6 @@
           <t>Canne planteuse</t>
         </is>
       </c>
-      <c r="C95">
-        <v>2</v>
-      </c>
-      <c r="D95">
-        <v>0</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2090,12 +1808,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C98">
-        <v>2</v>
-      </c>
-      <c r="D98">
-        <v>0</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2126,12 +1838,6 @@
           <t>Décortiqueur / dépailleur</t>
         </is>
       </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2198,12 +1904,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C104">
-        <v>4</v>
-      </c>
-      <c r="D104">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2252,12 +1952,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C107">
-        <v>4</v>
-      </c>
-      <c r="D107">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2288,12 +1982,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C109">
-        <v>1</v>
-      </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2306,12 +1994,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C110">
-        <v>3</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2324,12 +2006,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C111">
-        <v>4</v>
-      </c>
-      <c r="D111">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2342,12 +2018,6 @@
           <t>Râteau, fourche</t>
         </is>
       </c>
-      <c r="C112">
-        <v>4</v>
-      </c>
-      <c r="D112">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2378,12 +2048,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C114">
-        <v>1</v>
-      </c>
-      <c r="D114">
-        <v>0</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2413,12 +2077,6 @@
         <is>
           <t>Tracteur</t>
         </is>
-      </c>
-      <c r="C116">
-        <v>2</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_agri_equip_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -967,7 +967,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
